--- a/artfynd/Maskaure Maddagielas S, 27 ha artfynd.xlsx
+++ b/artfynd/Maskaure Maddagielas S, 27 ha artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY56"/>
+  <dimension ref="A1:AY57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5403,48 +5403,51 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135331414</v>
+        <v>135332491</v>
       </c>
       <c r="B44" t="n">
-        <v>91937</v>
+        <v>91995</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Maskaure maddagielas s, Pi lm</t>
+          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>635487</v>
+        <v>635420</v>
       </c>
       <c r="R44" t="n">
-        <v>7292003</v>
+        <v>7291943</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5473,7 +5476,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5483,7 +5486,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5492,18 +5495,19 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5514,48 +5518,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135330170</v>
+        <v>135331414</v>
       </c>
       <c r="B45" t="n">
-        <v>79373</v>
+        <v>91937</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Maskaure Maddagielas N+S_topo, Pi lm</t>
+          <t>Maskaure maddagielas s, Pi lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>635399</v>
+        <v>635487</v>
       </c>
       <c r="R45" t="n">
-        <v>7291941</v>
+        <v>7292003</v>
       </c>
       <c r="S45" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5584,7 +5588,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5594,7 +5598,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5609,12 +5613,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5625,7 +5629,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135332019</v>
+        <v>135330170</v>
       </c>
       <c r="B46" t="n">
         <v>79373</v>
@@ -5656,17 +5660,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+          <t>Maskaure Maddagielas N+S_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>635436</v>
+        <v>635399</v>
       </c>
       <c r="R46" t="n">
-        <v>7291953</v>
+        <v>7291941</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5695,7 +5699,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5705,7 +5709,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5720,12 +5724,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5736,7 +5740,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135332023</v>
+        <v>135332019</v>
       </c>
       <c r="B47" t="n">
         <v>79373</v>
@@ -5771,10 +5775,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>635499</v>
+        <v>635436</v>
       </c>
       <c r="R47" t="n">
-        <v>7291951</v>
+        <v>7291953</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5806,7 +5810,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5816,7 +5820,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5847,7 +5851,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135332024</v>
+        <v>135332023</v>
       </c>
       <c r="B48" t="n">
         <v>79373</v>
@@ -5882,13 +5886,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>635489</v>
+        <v>635499</v>
       </c>
       <c r="R48" t="n">
-        <v>7291940</v>
+        <v>7291951</v>
       </c>
       <c r="S48" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5917,7 +5921,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5927,7 +5931,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5958,7 +5962,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135332496</v>
+        <v>135332024</v>
       </c>
       <c r="B49" t="n">
         <v>79373</v>
@@ -5993,13 +5997,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>635492</v>
+        <v>635489</v>
       </c>
       <c r="R49" t="n">
-        <v>7291900</v>
+        <v>7291940</v>
       </c>
       <c r="S49" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6028,7 +6032,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6038,7 +6042,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6053,12 +6057,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -6069,53 +6073,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135331412</v>
+        <v>135332496</v>
       </c>
       <c r="B50" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Maskaure maddagielas s, Pi lm</t>
+          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>635494</v>
+        <v>635492</v>
       </c>
       <c r="R50" t="n">
-        <v>7292004</v>
+        <v>7291900</v>
       </c>
       <c r="S50" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6144,7 +6143,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6154,12 +6153,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6174,12 +6168,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -6190,7 +6184,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135331420</v>
+        <v>135331412</v>
       </c>
       <c r="B51" t="n">
         <v>57975</v>
@@ -6221,7 +6215,7 @@
       <c r="I51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6230,13 +6224,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>635511</v>
+        <v>635494</v>
       </c>
       <c r="R51" t="n">
-        <v>7292041</v>
+        <v>7292004</v>
       </c>
       <c r="S51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6265,7 +6259,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6275,12 +6269,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6311,7 +6305,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135331423</v>
+        <v>135331420</v>
       </c>
       <c r="B52" t="n">
         <v>57975</v>
@@ -6351,10 +6345,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>635482</v>
+        <v>635511</v>
       </c>
       <c r="R52" t="n">
-        <v>7291954</v>
+        <v>7292041</v>
       </c>
       <c r="S52" t="n">
         <v>3</v>
@@ -6386,7 +6380,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6396,7 +6390,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -6432,7 +6426,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135332027</v>
+        <v>135331423</v>
       </c>
       <c r="B53" t="n">
         <v>57975</v>
@@ -6461,19 +6455,24 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+          <t>Maskaure maddagielas s, Pi lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>635468</v>
+        <v>635482</v>
       </c>
       <c r="R53" t="n">
-        <v>7291882</v>
+        <v>7291954</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6502,7 +6501,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6512,12 +6511,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack, äldre</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6532,12 +6531,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6548,10 +6547,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135332020</v>
+        <v>135332027</v>
       </c>
       <c r="B54" t="n">
-        <v>79396</v>
+        <v>57975</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6559,21 +6558,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>260591</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6583,10 +6582,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>635462</v>
+        <v>635468</v>
       </c>
       <c r="R54" t="n">
-        <v>7291970</v>
+        <v>7291882</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6618,7 +6617,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6628,7 +6627,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6659,7 +6663,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135332021</v>
+        <v>135332020</v>
       </c>
       <c r="B55" t="n">
         <v>79396</v>
@@ -6694,10 +6698,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>635456</v>
+        <v>635462</v>
       </c>
       <c r="R55" t="n">
-        <v>7291978</v>
+        <v>7291970</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6729,7 +6733,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6739,7 +6743,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6770,7 +6774,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135332493</v>
+        <v>135332021</v>
       </c>
       <c r="B56" t="n">
         <v>79396</v>
@@ -6799,23 +6803,16 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>635459</v>
+        <v>635456</v>
       </c>
       <c r="R56" t="n">
-        <v>7291970</v>
+        <v>7291978</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6847,7 +6844,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6857,7 +6854,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6866,22 +6863,140 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135332493</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>635459</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7291970</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
           <t>Isak Falk Eliasson</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
+      <c r="AX57" t="inlineStr">
         <is>
           <t>Isak Falk Eliasson</t>
         </is>
       </c>
-      <c r="AY56" t="inlineStr">
+      <c r="AY57" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/Maskaure Maddagielas S, 27 ha artfynd.xlsx
+++ b/artfynd/Maskaure Maddagielas S, 27 ha artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AY58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6663,32 +6663,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135332020</v>
+        <v>135514135</v>
       </c>
       <c r="B55" t="n">
-        <v>79396</v>
+        <v>98066</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>260591</v>
+        <v>221941</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6698,13 +6698,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>635462</v>
+        <v>635466</v>
       </c>
       <c r="R55" t="n">
-        <v>7291970</v>
+        <v>7291977</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6743,7 +6743,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6758,23 +6758,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135332021</v>
+        <v>135332020</v>
       </c>
       <c r="B56" t="n">
         <v>79396</v>
@@ -6809,10 +6805,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>635456</v>
+        <v>635462</v>
       </c>
       <c r="R56" t="n">
-        <v>7291978</v>
+        <v>7291970</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6844,7 +6840,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6854,7 +6850,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6885,7 +6881,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135332493</v>
+        <v>135332021</v>
       </c>
       <c r="B57" t="n">
         <v>79396</v>
@@ -6914,23 +6910,16 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>635459</v>
+        <v>635456</v>
       </c>
       <c r="R57" t="n">
-        <v>7291970</v>
+        <v>7291978</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6962,7 +6951,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6972,7 +6961,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6981,22 +6970,140 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>135332493</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>635459</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7291970</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
           <t>Isak Falk Eliasson</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
+      <c r="AX58" t="inlineStr">
         <is>
           <t>Isak Falk Eliasson</t>
         </is>
       </c>
-      <c r="AY57" t="inlineStr">
+      <c r="AY58" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/Maskaure Maddagielas S, 27 ha artfynd.xlsx
+++ b/artfynd/Maskaure Maddagielas S, 27 ha artfynd.xlsx
@@ -6692,9 +6692,13 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+          <t>Maskaure Maddagielas S, Pi lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
@@ -6752,6 +6756,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6766,7 +6771,11 @@
           <t>Isak Falk Eliasson</t>
         </is>
       </c>
-      <c r="AY55" t="inlineStr"/>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">

--- a/artfynd/Maskaure Maddagielas S, 27 ha artfynd.xlsx
+++ b/artfynd/Maskaure Maddagielas S, 27 ha artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AZ58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332044</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331434</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,6 +1025,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332514</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1107,6 +1127,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110045455</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1223,6 +1248,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332041</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1334,6 +1364,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332042</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1445,6 +1480,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332510</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1556,6 +1596,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332512</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1683,6 +1728,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331427</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1794,6 +1844,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330172</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1905,6 +1960,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330173</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2016,6 +2076,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330175</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2127,6 +2192,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332039</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2238,6 +2308,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332488</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2359,6 +2434,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331410</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2475,6 +2555,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332036</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2586,6 +2671,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332028</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2697,6 +2787,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331431</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2808,6 +2903,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332038</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2919,6 +3019,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330176</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3035,6 +3140,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332032</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3146,6 +3256,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332034</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3257,6 +3372,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332500</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3368,6 +3488,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332501</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3479,6 +3604,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332506</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3600,6 +3730,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331430</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3716,6 +3851,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332033</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3827,6 +3967,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332029</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3938,6 +4083,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332030</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4049,6 +4199,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332031</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4160,6 +4315,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331418</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4271,6 +4431,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332022</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4382,6 +4547,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332025</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4493,6 +4663,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331422</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4604,6 +4779,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330168</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4715,6 +4895,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331415</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4826,6 +5011,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331416</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4937,6 +5127,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331419</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5046,6 +5241,11 @@
       <c r="AY40" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331421</t>
         </is>
       </c>
     </row>
@@ -5178,6 +5378,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332495</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5289,6 +5494,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332026</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5398,6 +5608,11 @@
       <c r="AY43" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332494</t>
         </is>
       </c>
     </row>
@@ -5515,6 +5730,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332491</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5626,6 +5846,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331414</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5737,6 +5962,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330170</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5848,6 +6078,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332019</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5959,6 +6194,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332023</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6070,6 +6310,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332024</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6181,6 +6426,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332496</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6302,6 +6552,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331412</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6423,6 +6678,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331420</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6544,6 +6804,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331423</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6658,6 +6923,11 @@
       <c r="AY54" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332027</t>
         </is>
       </c>
     </row>
@@ -6776,6 +7046,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135514135</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6887,6 +7162,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332020</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6998,6 +7278,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332021</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7117,8 +7402,72 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332493</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/Maskaure Maddagielas S, 27 ha artfynd.xlsx
+++ b/artfynd/Maskaure Maddagielas S, 27 ha artfynd.xlsx
@@ -948,7 +948,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+          <t>Maskaure Maddagielas S, Pi lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -1403,7 +1403,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+          <t>Maskaure Maddagielas S, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
@@ -1519,7 +1519,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+          <t>Maskaure Maddagielas S, Pi lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
@@ -2231,7 +2231,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+          <t>Maskaure Maddagielas S, Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
@@ -3295,7 +3295,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+          <t>Maskaure Maddagielas S, Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
@@ -3411,7 +3411,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+          <t>Maskaure Maddagielas S, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
@@ -3527,7 +3527,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+          <t>Maskaure Maddagielas S, Pi lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
@@ -5285,7 +5285,7 @@
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+          <t>Maskaure Maddagielas S, Pi lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
@@ -5533,7 +5533,7 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+          <t>Maskaure Maddagielas S, Pi lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
@@ -5652,7 +5652,7 @@
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+          <t>Maskaure Maddagielas S, Pi lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
@@ -6349,7 +6349,7 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+          <t>Maskaure Maddagielas S, Pi lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
@@ -7324,7 +7324,7 @@
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+          <t>Maskaure Maddagielas S, Pi lm</t>
         </is>
       </c>
       <c r="Q58" t="n">

--- a/artfynd/Maskaure Maddagielas S, 27 ha artfynd.xlsx
+++ b/artfynd/Maskaure Maddagielas S, 27 ha artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135332044</v>
       </c>
       <c r="B2" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135331434</v>
       </c>
       <c r="B3" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>135332514</v>
       </c>
       <c r="B4" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>135332041</v>
       </c>
       <c r="B6" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>135332042</v>
       </c>
       <c r="B7" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>135332510</v>
       </c>
       <c r="B8" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>135332512</v>
       </c>
       <c r="B9" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>135331427</v>
       </c>
       <c r="B10" t="n">
-        <v>58079</v>
+        <v>58084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>135330172</v>
       </c>
       <c r="B11" t="n">
-        <v>79050</v>
+        <v>79088</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>135330173</v>
       </c>
       <c r="B12" t="n">
-        <v>79050</v>
+        <v>79088</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>135330175</v>
       </c>
       <c r="B13" t="n">
-        <v>79050</v>
+        <v>79088</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>135332039</v>
       </c>
       <c r="B14" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>135332488</v>
       </c>
       <c r="B15" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>135331410</v>
       </c>
       <c r="B16" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>135332036</v>
       </c>
       <c r="B17" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>135332028</v>
       </c>
       <c r="B18" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>135331431</v>
       </c>
       <c r="B19" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>135332038</v>
       </c>
       <c r="B20" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>135330176</v>
       </c>
       <c r="B21" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>135332032</v>
       </c>
       <c r="B22" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>135332034</v>
       </c>
       <c r="B23" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>135332500</v>
       </c>
       <c r="B24" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>135332501</v>
       </c>
       <c r="B25" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>135332506</v>
       </c>
       <c r="B26" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>135331430</v>
       </c>
       <c r="B27" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>135332033</v>
       </c>
       <c r="B28" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>135332029</v>
       </c>
       <c r="B29" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>135332030</v>
       </c>
       <c r="B30" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>135332031</v>
       </c>
       <c r="B31" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
         <v>135331418</v>
       </c>
       <c r="B32" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>135332022</v>
       </c>
       <c r="B33" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>135332025</v>
       </c>
       <c r="B34" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>135331422</v>
       </c>
       <c r="B35" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>135330168</v>
       </c>
       <c r="B36" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>135331415</v>
       </c>
       <c r="B37" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>135331416</v>
       </c>
       <c r="B38" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>135331419</v>
       </c>
       <c r="B39" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>135331421</v>
       </c>
       <c r="B40" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>135332495</v>
       </c>
       <c r="B41" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>135332026</v>
       </c>
       <c r="B42" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>135332494</v>
       </c>
       <c r="B43" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>135332491</v>
       </c>
       <c r="B44" t="n">
-        <v>91995</v>
+        <v>92037</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>135331414</v>
       </c>
       <c r="B45" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>135330170</v>
       </c>
       <c r="B46" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         <v>135332019</v>
       </c>
       <c r="B47" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>135332023</v>
       </c>
       <c r="B48" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6205,7 +6205,7 @@
         <v>135332024</v>
       </c>
       <c r="B49" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         <v>135332496</v>
       </c>
       <c r="B50" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>135331412</v>
       </c>
       <c r="B51" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         <v>135331420</v>
       </c>
       <c r="B52" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6689,7 +6689,7 @@
         <v>135331423</v>
       </c>
       <c r="B53" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         <v>135332027</v>
       </c>
       <c r="B54" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>135514135</v>
       </c>
       <c r="B55" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         <v>135332020</v>
       </c>
       <c r="B56" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7173,7 +7173,7 @@
         <v>135332021</v>
       </c>
       <c r="B57" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>135332493</v>
       </c>
       <c r="B58" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Maddagielas S, 27 ha artfynd.xlsx
+++ b/artfynd/Maskaure Maddagielas S, 27 ha artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135332044</v>
       </c>
       <c r="B2" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135331434</v>
       </c>
       <c r="B3" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>135332514</v>
       </c>
       <c r="B4" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>135332041</v>
       </c>
       <c r="B6" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>135332042</v>
       </c>
       <c r="B7" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>135332510</v>
       </c>
       <c r="B8" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>135332512</v>
       </c>
       <c r="B9" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>135330172</v>
       </c>
       <c r="B11" t="n">
-        <v>79088</v>
+        <v>79115</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>135330173</v>
       </c>
       <c r="B12" t="n">
-        <v>79088</v>
+        <v>79115</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>135330175</v>
       </c>
       <c r="B13" t="n">
-        <v>79088</v>
+        <v>79115</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>135332039</v>
       </c>
       <c r="B14" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>135332488</v>
       </c>
       <c r="B15" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>135332036</v>
       </c>
       <c r="B17" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>135332028</v>
       </c>
       <c r="B18" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>135331431</v>
       </c>
       <c r="B19" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>135332038</v>
       </c>
       <c r="B20" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>135330176</v>
       </c>
       <c r="B21" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>135332032</v>
       </c>
       <c r="B22" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>135332034</v>
       </c>
       <c r="B23" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>135332500</v>
       </c>
       <c r="B24" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>135332501</v>
       </c>
       <c r="B25" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>135332506</v>
       </c>
       <c r="B26" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>135332029</v>
       </c>
       <c r="B29" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>135332030</v>
       </c>
       <c r="B30" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>135332031</v>
       </c>
       <c r="B31" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
         <v>135331418</v>
       </c>
       <c r="B32" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>135332022</v>
       </c>
       <c r="B33" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>135332025</v>
       </c>
       <c r="B34" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>135331422</v>
       </c>
       <c r="B35" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>135330168</v>
       </c>
       <c r="B36" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>135331415</v>
       </c>
       <c r="B37" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>135331416</v>
       </c>
       <c r="B38" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>135331419</v>
       </c>
       <c r="B39" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>135331421</v>
       </c>
       <c r="B40" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>135332495</v>
       </c>
       <c r="B41" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>135332026</v>
       </c>
       <c r="B42" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>135332494</v>
       </c>
       <c r="B43" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>135332491</v>
       </c>
       <c r="B44" t="n">
-        <v>92037</v>
+        <v>92064</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>135331414</v>
       </c>
       <c r="B45" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>135330170</v>
       </c>
       <c r="B46" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         <v>135332019</v>
       </c>
       <c r="B47" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>135332023</v>
       </c>
       <c r="B48" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6205,7 +6205,7 @@
         <v>135332024</v>
       </c>
       <c r="B49" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         <v>135332496</v>
       </c>
       <c r="B50" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>135514135</v>
       </c>
       <c r="B55" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         <v>135332020</v>
       </c>
       <c r="B56" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7173,7 +7173,7 @@
         <v>135332021</v>
       </c>
       <c r="B57" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>135332493</v>
       </c>
       <c r="B58" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Maddagielas S, 27 ha artfynd.xlsx
+++ b/artfynd/Maskaure Maddagielas S, 27 ha artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110045455</v>
+        <v>135332044</v>
       </c>
       <c r="B2" t="n">
-        <v>91909</v>
+        <v>79520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nymoran-brännan n, Pi lm</t>
+          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>635286</v>
+        <v>635160</v>
       </c>
       <c r="R2" t="n">
-        <v>7291447</v>
+        <v>7291723</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-06-22</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-06-22</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,24 +780,6693 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332044</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135331434</v>
+      </c>
+      <c r="B3" t="n">
+        <v>92044</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Maskaure maddagielas s, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>635278</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7291791</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331434</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135332514</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92044</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Maskaure Maddagielas S, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>635282</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7291795</v>
+      </c>
+      <c r="S4" t="n">
+        <v>9</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332514</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>110045455</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nymoran-brännan n, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>635286</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7291447</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-06-22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-06-22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Robert Sandberg</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Jonas Nordenström</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr">
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/110045455</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135332041</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>635267</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7291732</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På gammal tall</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332041</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135332042</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>635261</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7291738</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332042</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135332510</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Maskaure Maddagielas S, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>635303</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7291780</v>
+      </c>
+      <c r="S8" t="n">
+        <v>7</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332510</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135332512</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Maskaure Maddagielas S, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>635272</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7291815</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332512</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135331427</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58084</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Maskaure maddagielas s, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>635170</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7291658</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331427</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135330172</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>228654</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Grå renlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cladonia rangiferina</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Maskaure Maddagielas N+S_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>635279</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7291743</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330172</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135330173</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>228654</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grå renlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cladonia rangiferina</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Maskaure Maddagielas N+S_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>635222</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7291711</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330173</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135330175</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>228654</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Grå renlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cladonia rangiferina</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Maskaure Maddagielas N+S_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>635280</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7291498</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330175</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135332039</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>635325</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7291638</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332039</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135332488</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Maskaure Maddagielas S, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>635351</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7291937</v>
+      </c>
+      <c r="S15" t="n">
+        <v>7</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332488</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135331410</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Maskaure maddagielas s, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>635336</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7291909</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331410</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135332036</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92319</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>658</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>635613</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7291542</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På gammal granlåga</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332036</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135332028</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79520</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>864</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>635509</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7291671</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332028</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135331431</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Maskaure maddagielas s, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>635682</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7291445</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331431</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135332038</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>635611</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7291541</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332038</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135330176</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Maskaure Maddagielas N+S_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>635564</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7291497</v>
+      </c>
+      <c r="S21" t="n">
+        <v>17</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330176</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135332032</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>635614</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7291570</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332032</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135332034</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>635596</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7291529</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332034</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135332500</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Maskaure Maddagielas S, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>635459</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7291735</v>
+      </c>
+      <c r="S24" t="n">
+        <v>18</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332500</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135332501</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Maskaure Maddagielas S, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>635480</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7291696</v>
+      </c>
+      <c r="S25" t="n">
+        <v>6</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332501</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135332506</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Maskaure Maddagielas S, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>635512</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7291470</v>
+      </c>
+      <c r="S26" t="n">
+        <v>12</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332506</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135331430</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Maskaure maddagielas s, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>635683</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7291447</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331430</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135332033</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>635616</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7291548</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på gammal gran, äldre</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332033</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135332029</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>635509</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7291671</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332029</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135332030</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>635507</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7291665</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332030</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135332031</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>635507</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7291657</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332031</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135331418</v>
+      </c>
+      <c r="B32" t="n">
+        <v>92319</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>658</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Maskaure maddagielas s, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>635503</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7292026</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331418</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135332022</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79520</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>864</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>635487</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7291966</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332022</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135332025</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79520</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>864</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>635473</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7291963</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332025</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135331422</v>
+      </c>
+      <c r="B35" t="n">
+        <v>92044</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Maskaure maddagielas s, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>635483</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7291954</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331422</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135330168</v>
+      </c>
+      <c r="B36" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Maskaure Maddagielas N+S_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>635387</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7291934</v>
+      </c>
+      <c r="S36" t="n">
+        <v>8</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330168</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135331415</v>
+      </c>
+      <c r="B37" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Maskaure maddagielas s, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>635491</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7292002</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331415</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135331416</v>
+      </c>
+      <c r="B38" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Maskaure maddagielas s, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>635496</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7292028</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331416</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135331419</v>
+      </c>
+      <c r="B39" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Maskaure maddagielas s, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>635503</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7292027</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331419</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135331421</v>
+      </c>
+      <c r="B40" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Maskaure maddagielas s, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>635498</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7292043</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331421</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135332495</v>
+      </c>
+      <c r="B41" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Maskaure Maddagielas S, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>635515</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7291931</v>
+      </c>
+      <c r="S41" t="n">
+        <v>9</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>på stående död ved</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332495</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135332026</v>
+      </c>
+      <c r="B42" t="n">
+        <v>83292</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>635515</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7291938</v>
+      </c>
+      <c r="S42" t="n">
+        <v>11</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332026</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135332494</v>
+      </c>
+      <c r="B43" t="n">
+        <v>83292</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Maskaure Maddagielas S, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>635488</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7291963</v>
+      </c>
+      <c r="S43" t="n">
+        <v>9</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332494</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135332491</v>
+      </c>
+      <c r="B44" t="n">
+        <v>92069</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Maskaure Maddagielas S, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>635420</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7291943</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332491</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135331414</v>
+      </c>
+      <c r="B45" t="n">
+        <v>92011</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Maskaure maddagielas s, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>635487</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7292003</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331414</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135330170</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Maskaure Maddagielas N+S_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>635399</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7291941</v>
+      </c>
+      <c r="S46" t="n">
+        <v>17</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330170</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135332019</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>635436</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7291953</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332019</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135332023</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>635499</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7291951</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332023</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>135332024</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>635489</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7291940</v>
+      </c>
+      <c r="S49" t="n">
+        <v>6</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332024</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135332496</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Maskaure Maddagielas S, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>635492</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7291900</v>
+      </c>
+      <c r="S50" t="n">
+        <v>8</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332496</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>135331412</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Maskaure maddagielas s, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>635494</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7292004</v>
+      </c>
+      <c r="S51" t="n">
+        <v>4</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331412</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135331420</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Maskaure maddagielas s, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>635511</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7292041</v>
+      </c>
+      <c r="S52" t="n">
+        <v>3</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331420</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>135331423</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Maskaure maddagielas s, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>635482</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7291954</v>
+      </c>
+      <c r="S53" t="n">
+        <v>3</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331423</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>135332027</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>635468</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7291882</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332027</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>135514135</v>
+      </c>
+      <c r="B55" t="n">
+        <v>98142</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Maskaure Maddagielas S, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>635466</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7291977</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135514135</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135332020</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>635462</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7291970</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332020</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135332021</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Ons Gr 4_Maskaure Maddagielas N+S_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>635456</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7291978</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332021</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>135332493</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Maskaure Maddagielas S, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>635459</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7291970</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332493</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/Maskaure Maddagielas S, 27 ha artfynd.xlsx
+++ b/artfynd/Maskaure Maddagielas S, 27 ha artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>135331434</v>
       </c>
       <c r="B3" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>135332514</v>
       </c>
       <c r="B4" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>135332036</v>
       </c>
       <c r="B17" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>135331431</v>
       </c>
       <c r="B19" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>135332038</v>
       </c>
       <c r="B20" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
         <v>135331418</v>
       </c>
       <c r="B32" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>135331422</v>
       </c>
       <c r="B35" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>135330168</v>
       </c>
       <c r="B36" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>135331415</v>
       </c>
       <c r="B37" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>135331416</v>
       </c>
       <c r="B38" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>135331419</v>
       </c>
       <c r="B39" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>135331421</v>
       </c>
       <c r="B40" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>135332495</v>
       </c>
       <c r="B41" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>135332491</v>
       </c>
       <c r="B44" t="n">
-        <v>92069</v>
+        <v>92071</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>135331414</v>
       </c>
       <c r="B45" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>135514135</v>
       </c>
       <c r="B55" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Maddagielas S, 27 ha artfynd.xlsx
+++ b/artfynd/Maskaure Maddagielas S, 27 ha artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>135332514</v>
       </c>
       <c r="B4" t="n">
-        <v>92046</v>
+        <v>92060</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>135332500</v>
       </c>
       <c r="B24" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>135332494</v>
       </c>
       <c r="B43" t="n">
-        <v>83292</v>
+        <v>83294</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>135332491</v>
       </c>
       <c r="B44" t="n">
-        <v>92071</v>
+        <v>92085</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>135514135</v>
       </c>
       <c r="B55" t="n">
-        <v>98144</v>
+        <v>98161</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Maddagielas S, 27 ha artfynd.xlsx
+++ b/artfynd/Maskaure Maddagielas S, 27 ha artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>135332514</v>
       </c>
       <c r="B4" t="n">
-        <v>92060</v>
+        <v>92061</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>135332500</v>
       </c>
       <c r="B24" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>135332494</v>
       </c>
       <c r="B43" t="n">
-        <v>83294</v>
+        <v>83311</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>135332491</v>
       </c>
       <c r="B44" t="n">
-        <v>92085</v>
+        <v>92086</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>135514135</v>
       </c>
       <c r="B55" t="n">
-        <v>98161</v>
+        <v>98162</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
